--- a/samples/output/sample_sales_field_report.xlsx
+++ b/samples/output/sample_sales_field_report.xlsx
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Count / Frequency Table — not recommended for visualization ⚠ All unique — likely ID column</t>
+          <t>Count / Frequency Table — not recommended for visualization</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
